--- a/Result/profitability/6416.xlsx
+++ b/Result/profitability/6416.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM49"/>
+  <dimension ref="A1:AM50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6653,6 +6653,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>6416</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1333</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1011</v>
+      </c>
+      <c r="E50" t="n">
+        <v>322</v>
+      </c>
+      <c r="F50" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="G50" t="n">
+        <v>142</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>10.67%</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>5</v>
+      </c>
+      <c r="J50" t="n">
+        <v>147</v>
+      </c>
+      <c r="K50" t="n">
+        <v>114</v>
+      </c>
+      <c r="L50" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="N50" t="n">
+        <v>23.73125</v>
+      </c>
+      <c r="O50" t="n">
+        <v>1</v>
+      </c>
+      <c r="P50" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>1</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
+      </c>
+      <c r="V50" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0.1481481481481481</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>-1.490000000000002</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>-0.05804440981690695</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>1.066666666666667</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0.06519823788546253</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK50" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
